--- a/data/trans_orig/P1001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472112</t>
+          <t>472391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487025</t>
+          <t>487303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445783</t>
+          <t>446619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460336</t>
+          <t>460520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925198</t>
+          <t>922947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>944643</t>
+          <t>943964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60091</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>53046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90248</t>
+          <t>86314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>700083</t>
+          <t>699531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>719520</t>
+          <t>719319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>565403</t>
+          <t>564477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591736</t>
+          <t>591367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270734</t>
+          <t>1274668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1306692</t>
+          <t>1307936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38051</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>60124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>58192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91362</t>
+          <t>90560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600617</t>
+          <t>599611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621997</t>
+          <t>620931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>628976</t>
+          <t>629620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655430</t>
+          <t>656352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237050</t>
+          <t>1237852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1271937</t>
+          <t>1270220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43799</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73732</t>
+          <t>73743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>73785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112766</t>
+          <t>110743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>475348</t>
+          <t>472421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>497033</t>
+          <t>495997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441910</t>
+          <t>441899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471188</t>
+          <t>470950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922023</t>
+          <t>924046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>960215</t>
+          <t>961004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58180</t>
+          <t>58035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61670</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96281</t>
+          <t>94204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>343306</t>
+          <t>342675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364121</t>
+          <t>364372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345806</t>
+          <t>345951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370635</t>
+          <t>371078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>694415</t>
+          <t>696492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729026</t>
+          <t>729925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>37665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62129</t>
+          <t>61679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66525</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101360</t>
+          <t>103688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246349</t>
+          <t>245725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268033</t>
+          <t>266907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280805</t>
+          <t>281255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>305269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>534157</t>
+          <t>531829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568992</t>
+          <t>567312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48281</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>79976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79726</t>
+          <t>79860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116850</t>
+          <t>116813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162955</t>
+          <t>163349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184486</t>
+          <t>184320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254538</t>
+          <t>253932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285627</t>
+          <t>284819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>426941</t>
+          <t>426978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>464065</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>171962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>225005</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>283244</t>
+          <t>285475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>354868</t>
+          <t>353205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>516514</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>475327</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>557935</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>516514</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>472859</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>560462</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3051538</t>
+          <t>3047829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3104090</t>
+          <t>3104581</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3024329</t>
+          <t>3025992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3095953</t>
+          <t>3093722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6139227</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6097806</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6180414</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6139227</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6095279</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6182882</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438533</t>
+          <t>437586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449628</t>
+          <t>449587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401335</t>
+          <t>398786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418724</t>
+          <t>418109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>844146</t>
+          <t>842946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864881</t>
+          <t>864102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>33375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>22562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>47162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70790</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654457</t>
+          <t>653712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>674684</t>
+          <t>674764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564222</t>
+          <t>563093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587239</t>
+          <t>587693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1226552</t>
+          <t>1226948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1255981</t>
+          <t>1256931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51444</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67075</t>
+          <t>65980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102414</t>
+          <t>102005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100406</t>
+          <t>98883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142794</t>
+          <t>142534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629482</t>
+          <t>630270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654635</t>
+          <t>656003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608436</t>
+          <t>608845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643775</t>
+          <t>644870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248981</t>
+          <t>1249241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291369</t>
+          <t>1292892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>58225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67741</t>
+          <t>66609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101845</t>
+          <t>102314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>102452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149808</t>
+          <t>147456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>554863</t>
+          <t>555338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>583444</t>
+          <t>583582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>514354</t>
+          <t>513885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548458</t>
+          <t>549590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1079954</t>
+          <t>1082306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1125828</t>
+          <t>1127310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76633</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110683</t>
+          <t>108013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111574</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156356</t>
+          <t>155706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>375590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398776</t>
+          <t>399405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336062</t>
+          <t>338732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370112</t>
+          <t>371759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>719818</t>
+          <t>720468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>764600</t>
+          <t>762022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50193</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98806</t>
+          <t>97842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98737</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139492</t>
+          <t>139429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259593</t>
+          <t>257203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283036</t>
+          <t>282657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254245</t>
+          <t>255209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285490</t>
+          <t>285769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523345</t>
+          <t>523408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>564100</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71206</t>
+          <t>69736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109995</t>
+          <t>110561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149368</t>
+          <t>149019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161021</t>
+          <t>162978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>210383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178645</t>
+          <t>180115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>206634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>239611</t>
+          <t>239960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278984</t>
+          <t>278418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>430356</t>
+          <t>428447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477809</t>
+          <t>475852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>213601</t>
+          <t>211723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>277081</t>
+          <t>274717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480563</t>
+          <t>480889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>566098</t>
+          <t>568669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>709853</t>
+          <t>710869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>815980</t>
+          <t>817586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3147707</t>
+          <t>3150071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3211187</t>
+          <t>3213065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2990211</t>
+          <t>2987640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3075746</t>
+          <t>3075420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6165117</t>
+          <t>6163511</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6271244</t>
+          <t>6270228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401645</t>
+          <t>401199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415116</t>
+          <t>414702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374764</t>
+          <t>374546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388906</t>
+          <t>388703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>781799</t>
+          <t>783143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>801726</t>
+          <t>801506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40173</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67121</t>
+          <t>69014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>552280</t>
+          <t>551277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573907</t>
+          <t>573575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>526256</t>
+          <t>526425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>545712</t>
+          <t>545505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1086919</t>
+          <t>1085026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113867</t>
+          <t>1114093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>33422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>60887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94747</t>
+          <t>95784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624420</t>
+          <t>625675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647529</t>
+          <t>647655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>602054</t>
+          <t>603740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628036</t>
+          <t>627964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1235736</t>
+          <t>1234699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1270536</t>
+          <t>1269596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>54171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84985</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91354</t>
+          <t>93069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134058</t>
+          <t>134127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586534</t>
+          <t>586159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613633</t>
+          <t>613957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564092</t>
+          <t>564736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>596412</t>
+          <t>594906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161067</t>
+          <t>1160998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1203771</t>
+          <t>1202056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>45427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>71633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108402</t>
+          <t>106826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100210</t>
+          <t>101181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146220</t>
+          <t>145543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431614</t>
+          <t>432491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455021</t>
+          <t>455085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388447</t>
+          <t>390023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425000</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>828547</t>
+          <t>829224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>874557</t>
+          <t>873586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>67357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99091</t>
+          <t>99285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131211</t>
+          <t>133193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293405</t>
+          <t>293205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315333</t>
+          <t>314639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278671</t>
+          <t>278477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309146</t>
+          <t>310405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580881</t>
+          <t>578899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>621462</t>
+          <t>617907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130853</t>
+          <t>132686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119658</t>
+          <t>120220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169028</t>
+          <t>167775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>212982</t>
+          <t>212751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234058</t>
+          <t>232773</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269316</t>
+          <t>267483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310837</t>
+          <t>307727</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>488139</t>
+          <t>489392</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537509</t>
+          <t>536947</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>181184</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>236112</t>
+          <t>236610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>393719</t>
+          <t>390919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>471155</t>
+          <t>475836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592027</t>
+          <t>595029</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>686199</t>
+          <t>687165</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3158238</t>
+          <t>3157740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3213166</t>
+          <t>3214462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3073387</t>
+          <t>3068706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3150823</t>
+          <t>3153623</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6252693</t>
+          <t>6251727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6346865</t>
+          <t>6343863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>44182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60396</t>
+          <t>59480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366860</t>
+          <t>371308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396672</t>
+          <t>396658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271452</t>
+          <t>269018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299380</t>
+          <t>299003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652791</t>
+          <t>653707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690442</t>
+          <t>690784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44482</t>
+          <t>44230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57609</t>
+          <t>56187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401450</t>
+          <t>399955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419586</t>
+          <t>419511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467022</t>
+          <t>467274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495996</t>
+          <t>495029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877442</t>
+          <t>878864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>909441</t>
+          <t>909154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>44424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41506</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>49104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77694</t>
+          <t>78789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491654</t>
+          <t>491914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515748</t>
+          <t>515036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500962</t>
+          <t>501586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518635</t>
+          <t>519496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1001112</t>
+          <t>1000017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1030636</t>
+          <t>1029702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67935</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>51330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83899</t>
+          <t>82637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137515</t>
+          <t>138465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819851</t>
+          <t>820783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868563</t>
+          <t>869797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628337</t>
+          <t>629599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660965</t>
+          <t>660906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1462508</t>
+          <t>1461558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1533226</t>
+          <t>1534005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>32468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85064</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>98629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133431</t>
+          <t>133627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505013</t>
+          <t>505620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>528054</t>
+          <t>528766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462519</t>
+          <t>462566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486691</t>
+          <t>486161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975386</t>
+          <t>975190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1010404</t>
+          <t>1010188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>96816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42627</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119039</t>
+          <t>117848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331322</t>
+          <t>329967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>347400</t>
+          <t>346331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>512347</t>
+          <t>511552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583668</t>
+          <t>582420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>856924</t>
+          <t>858115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>933336</t>
+          <t>934522</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>98074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124358</t>
+          <t>126183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127960</t>
+          <t>127814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159591</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239136</t>
+          <t>239842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256973</t>
+          <t>256912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300081</t>
+          <t>298256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326622</t>
+          <t>326365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546971</t>
+          <t>546962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578602</t>
+          <t>578748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153091</t>
+          <t>150804</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230943</t>
+          <t>230107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>325389</t>
+          <t>323034</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>436584</t>
+          <t>440327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>516011</t>
+          <t>514146</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>654703</t>
+          <t>652784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3227668</t>
+          <t>3228504</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3305520</t>
+          <t>3307807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3223215</t>
+          <t>3219472</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3334410</t>
+          <t>3336765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6463706</t>
+          <t>6465625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6602398</t>
+          <t>6604263</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12628</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21178</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12628</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6969</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20870</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472391</t>
+          <t>472275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487303</t>
+          <t>487599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,49 +861,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>454861</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>446311</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>461062</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>454861</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>446619</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>460520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>964</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>922947</t>
+          <t>922924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943964</t>
+          <t>944936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53046</t>
+          <t>53450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86314</t>
+          <t>88182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>699531</t>
+          <t>700773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>719319</t>
+          <t>719231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564477</t>
+          <t>565229</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591367</t>
+          <t>591406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1274668</t>
+          <t>1272800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1307936</t>
+          <t>1307532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60124</t>
+          <t>60922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58192</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90560</t>
+          <t>90541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599611</t>
+          <t>598222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620931</t>
+          <t>620871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629620</t>
+          <t>628822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656352</t>
+          <t>655353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237852</t>
+          <t>1237871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1270220</t>
+          <t>1272702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73743</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73785</t>
+          <t>73941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110743</t>
+          <t>109632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>472421</t>
+          <t>474596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>495997</t>
+          <t>496506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441899</t>
+          <t>441591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470950</t>
+          <t>470520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>924046</t>
+          <t>925157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>961004</t>
+          <t>960848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60771</t>
+          <t>61532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>93311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342675</t>
+          <t>343660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364372</t>
+          <t>364326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345951</t>
+          <t>345877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371078</t>
+          <t>370410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>696492</t>
+          <t>697385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729925</t>
+          <t>729164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>47368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37665</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61679</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68205</t>
+          <t>68446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>100644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245725</t>
+          <t>245215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>267531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281255</t>
+          <t>281272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305269</t>
+          <t>305893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531829</t>
+          <t>534873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>567312</t>
+          <t>567071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>46683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>47795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79976</t>
+          <t>77958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79860</t>
+          <t>82197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116813</t>
+          <t>117331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163349</t>
+          <t>163200</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184320</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>253932</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>286113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>426978</t>
+          <t>426460</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463931</t>
+          <t>461594</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>228714</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>353205</t>
+          <t>353412</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>475327</t>
+          <t>473518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>557935</t>
+          <t>564186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3047829</t>
+          <t>3049425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3104581</t>
+          <t>3104622</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3025992</t>
+          <t>3025785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3093722</t>
+          <t>3094942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6097806</t>
+          <t>6091555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6180414</t>
+          <t>6182223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437586</t>
+          <t>438280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449587</t>
+          <t>449526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>398786</t>
+          <t>400159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418109</t>
+          <t>417784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>842946</t>
+          <t>843807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864102</t>
+          <t>865383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47162</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>653712</t>
+          <t>654854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>674764</t>
+          <t>674587</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>563093</t>
+          <t>562187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587693</t>
+          <t>586893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1226948</t>
+          <t>1225951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256931</t>
+          <t>1257106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50656</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65980</t>
+          <t>64595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102005</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>98483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>142357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630270</t>
+          <t>629569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656003</t>
+          <t>654301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608845</t>
+          <t>610253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>646255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249241</t>
+          <t>1249418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1292892</t>
+          <t>1293292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>65462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102314</t>
+          <t>101464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102452</t>
+          <t>105329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147456</t>
+          <t>150794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>555338</t>
+          <t>555899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>583582</t>
+          <t>583417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513885</t>
+          <t>514735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549590</t>
+          <t>550737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1082306</t>
+          <t>1078968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1127310</t>
+          <t>1124433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74986</t>
+          <t>74207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108013</t>
+          <t>111651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>114471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155706</t>
+          <t>157213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375590</t>
+          <t>374223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399405</t>
+          <t>398454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338732</t>
+          <t>335094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371759</t>
+          <t>372538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720468</t>
+          <t>718961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762022</t>
+          <t>761703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67282</t>
+          <t>65601</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>96107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>98857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139429</t>
+          <t>139996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257203</t>
+          <t>259319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282657</t>
+          <t>283948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255209</t>
+          <t>256944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285769</t>
+          <t>287450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523408</t>
+          <t>522841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>565643</t>
+          <t>563980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43217</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110561</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149019</t>
+          <t>150437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>162853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210383</t>
+          <t>211469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180115</t>
+          <t>178991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206634</t>
+          <t>207484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>239960</t>
+          <t>238542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278418</t>
+          <t>278228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428447</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>475852</t>
+          <t>475977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211723</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>274717</t>
+          <t>280066</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480889</t>
+          <t>483844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>568669</t>
+          <t>565020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>710869</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>817586</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3150071</t>
+          <t>3144722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3213065</t>
+          <t>3209795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2987640</t>
+          <t>2991289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3075420</t>
+          <t>3072465</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6163511</t>
+          <t>6160143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6270228</t>
+          <t>6269347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401199</t>
+          <t>401873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414702</t>
+          <t>415245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374546</t>
+          <t>374848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388703</t>
+          <t>389293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783143</t>
+          <t>782011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>801506</t>
+          <t>801101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37119</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69014</t>
+          <t>68984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>551277</t>
+          <t>552043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573575</t>
+          <t>572495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>526425</t>
+          <t>526056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>545505</t>
+          <t>545442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1085026</t>
+          <t>1085056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1114093</t>
+          <t>1115207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33422</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57646</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625675</t>
+          <t>624192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647655</t>
+          <t>647369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603740</t>
+          <t>602340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627964</t>
+          <t>628252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1234699</t>
+          <t>1236157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1269596</t>
+          <t>1270120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59889</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54171</t>
+          <t>52921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>87134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93069</t>
+          <t>92314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134127</t>
+          <t>138257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586159</t>
+          <t>584893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613957</t>
+          <t>612978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564736</t>
+          <t>561943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594906</t>
+          <t>596156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160998</t>
+          <t>1156868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1202056</t>
+          <t>1202811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71633</t>
+          <t>71943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106826</t>
+          <t>108348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101181</t>
+          <t>101375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145543</t>
+          <t>142051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>432491</t>
+          <t>433907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455085</t>
+          <t>455496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390023</t>
+          <t>388501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425216</t>
+          <t>424906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>829224</t>
+          <t>832716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>873586</t>
+          <t>873392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67357</t>
+          <t>66418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99285</t>
+          <t>100215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94185</t>
+          <t>92543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133193</t>
+          <t>132574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293205</t>
+          <t>293004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314639</t>
+          <t>314168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278477</t>
+          <t>277547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310405</t>
+          <t>311344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578899</t>
+          <t>579518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>617907</t>
+          <t>619549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92442</t>
+          <t>88854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132686</t>
+          <t>130283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120220</t>
+          <t>120878</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167775</t>
+          <t>166599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>213384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232773</t>
+          <t>233809</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267483</t>
+          <t>269886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>307727</t>
+          <t>311315</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>489392</t>
+          <t>490568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>536947</t>
+          <t>536289</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179888</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>236610</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390919</t>
+          <t>388455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>475836</t>
+          <t>477619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>595029</t>
+          <t>589503</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>687165</t>
+          <t>686955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3157740</t>
+          <t>3158526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3214462</t>
+          <t>3215919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3068706</t>
+          <t>3066923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3153623</t>
+          <t>3156087</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6251727</t>
+          <t>6251937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6343863</t>
+          <t>6349389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -9665,17 +9665,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>47741</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59480</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -9778,17 +9778,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>388712</t>
+          <t>396304</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371308</t>
+          <t>379639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396658</t>
+          <t>404541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287081</t>
+          <t>333566</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269018</t>
+          <t>314771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299003</t>
+          <t>346011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>675793</t>
+          <t>729870</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>653707</t>
+          <t>705156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690784</t>
+          <t>744973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>43032</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413627</t>
+          <t>465197</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399955</t>
+          <t>452716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419511</t>
+          <t>472675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>482570</t>
+          <t>469744</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467274</t>
+          <t>453851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495029</t>
+          <t>479914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>896197</t>
+          <t>934941</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>878864</t>
+          <t>918495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>909154</t>
+          <t>948724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>47578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31477</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>28610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62415</t>
+          <t>70481</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49104</t>
+          <t>57092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505400</t>
+          <t>588169</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491914</t>
+          <t>573259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515036</t>
+          <t>598382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>510991</t>
+          <t>584325</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501586</t>
+          <t>573349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519496</t>
+          <t>593529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1016391</t>
+          <t>1172495</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1000017</t>
+          <t>1155996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1029702</t>
+          <t>1185884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67003</t>
+          <t>61661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64362</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82637</t>
+          <t>78397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>107940</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>93540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138465</t>
+          <t>131180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>844207</t>
+          <t>655422</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>820783</t>
+          <t>638956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869797</t>
+          <t>667106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>647874</t>
+          <t>670335</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629599</t>
+          <t>657799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660906</t>
+          <t>682834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1492083</t>
+          <t>1325757</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1461558</t>
+          <t>1305633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1534005</t>
+          <t>1343273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712236</t>
+          <t>736196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712236</t>
+          <t>736196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712236</t>
+          <t>736196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600023</t>
+          <t>1436813</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600023</t>
+          <t>1436813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600023</t>
+          <t>1436813</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>43657</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>56973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>72338</t>
+          <t>82038</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61422</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>114547</t>
+          <t>125695</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98629</t>
+          <t>108677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133627</t>
+          <t>143237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>519025</t>
+          <t>565689</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505620</t>
+          <t>552373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>528766</t>
+          <t>576460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>475245</t>
+          <t>526499</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>511944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486161</t>
+          <t>539434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>994270</t>
+          <t>1092188</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975190</t>
+          <t>1074646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1010188</t>
+          <t>1109206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>31152</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>41546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60899</t>
+          <t>68749</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>57657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96816</t>
+          <t>80720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>99901</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>85479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>116017</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>339088</t>
+          <t>375341</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>329967</t>
+          <t>364947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>346331</t>
+          <t>383129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>547469</t>
+          <t>370417</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>358446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582420</t>
+          <t>381509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>886558</t>
+          <t>745759</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>858115</t>
+          <t>729643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>934522</t>
+          <t>760181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>37255</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>110872</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>110093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126183</t>
+          <t>138227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>143435</t>
+          <t>160516</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127814</t>
+          <t>142890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159600</t>
+          <t>177764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>249560</t>
+          <t>272328</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239842</t>
+          <t>262852</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256912</t>
+          <t>281411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>313567</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298256</t>
+          <t>324945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326365</t>
+          <t>353079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>563127</t>
+          <t>612239</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546962</t>
+          <t>594991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578748</t>
+          <t>629865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424439</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424439</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424439</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706562</t>
+          <t>772755</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706562</t>
+          <t>772755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706562</t>
+          <t>772755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150804</t>
+          <t>185392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230107</t>
+          <t>243544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>323034</t>
+          <t>404522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>440327</t>
+          <t>472033</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>514146</t>
+          <t>605652</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>652784</t>
+          <t>698833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3259621</t>
+          <t>3318451</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3228504</t>
+          <t>3288016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3307807</t>
+          <t>3346168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3264798</t>
+          <t>3294797</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3219472</t>
+          <t>3260773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3336765</t>
+          <t>3328284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6524418</t>
+          <t>6613248</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6465625</t>
+          <t>6565533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6604263</t>
+          <t>6658714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>91,66%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
